--- a/Database/Production_Line.xlsx
+++ b/Database/Production_Line.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I441"/>
+  <dimension ref="A1:I481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9163,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Defeated_Timeout</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -20327,26 +20327,1806 @@
         </is>
       </c>
     </row>
-    <row r="442" ht="18" customHeight="1"/>
-    <row r="443" ht="18" customHeight="1"/>
-    <row r="444" ht="18" customHeight="1"/>
-    <row r="445" ht="18" customHeight="1"/>
-    <row r="446" ht="18" customHeight="1"/>
-    <row r="447" ht="18" customHeight="1"/>
-    <row r="448" ht="18" customHeight="1"/>
-    <row r="449" ht="18" customHeight="1"/>
-    <row r="450" ht="18" customHeight="1"/>
-    <row r="451" ht="18" customHeight="1"/>
-    <row r="452" ht="18" customHeight="1"/>
-    <row r="453" ht="18" customHeight="1"/>
-    <row r="454" ht="18" customHeight="1"/>
-    <row r="455" ht="18" customHeight="1"/>
-    <row r="456" ht="18" customHeight="1"/>
-    <row r="457" ht="18" customHeight="1"/>
-    <row r="458" ht="18" customHeight="1"/>
-    <row r="459" ht="18" customHeight="1"/>
-    <row r="460" ht="18" customHeight="1"/>
-    <row r="461" ht="18" customHeight="1"/>
+    <row r="442" ht="18" customHeight="1">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0081</t>
+        </is>
+      </c>
+      <c r="B442" s="5" t="n">
+        <v>46141.66572011574</v>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Armillary Navigation Sphere</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>An ornate armillary sphere with rotating brass rings orbiting a central Starlight Jade core, concentric Obsidian bands etched with constellation maps, floating crystalline navigation markers suspended in mid-rotation, dark academia aesthetic with astronomical precision, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, sharp focus, wide cinematic angle, dramatic side lighting, hyper-detailed mentor-grade object design, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>celestial navigation sphere, armillary sphere art, astronomical instrument poster, dark academia decor, constellation map wall art, brass and jade celestial globe, vintage astronomy print, scholar study decoration, astrological navigation tool, mentor-grade collectible, premium vertical poster, museum-quality celestial art</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="18" customHeight="1">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0082</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="n">
+        <v>46141.66657107639</v>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Armillary Codex</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>An ornate armillary sphere with rotating brass rings surrounding an open ancient book with constellation maps, pages made of translucent Amber sheets with glowing star charts, floating golden stardust particles orbiting the rings, warm academic library lighting, mechanical gears visible at joints, crystalline navigation tools embedded in rings, aged brass patina with micro-engraved astronomical symbols, layered translucent depth, subtle internal bioluminescent glow from book pages, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>astrological globe poster, celestial navigation art, brass armillary sphere, academic astronomy decor, amber constellation map, vintage scientific instrument, museum quality wall art, astrology scholar gift, mechanical cosmos print, golden stardust design, antique astronomy poster</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="18" customHeight="1">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0083</t>
+        </is>
+      </c>
+      <c r="B444" s="5" t="n">
+        <v>46141.66662832176</v>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Cosmic Lotus Observatory</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>A blooming mechanical lotus flower with brass petals that unfold to reveal crystalline star charts, center core made of translucent Amber with glowing celestial coordinates, golden stardust emanating from stamens, each petal engraved with zodiac symbols and planetary orbits, warm academic lighting, sharp focus, botanical-astronomical hybrid design, aged brass with kintsugi-like amber veins, floating accent fragments, layered translucent depth, subtle internal bioluminescent glow, refined handcrafted edge bevels, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>botanical astronomy art, mechanical lotus poster, brass flower celestial, academic astrology decor, amber star chart, steampunk botanical print, cosmic lotus wall art, zodiac flower design, golden stardust botanical, museum grade nature astronomy</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="18" customHeight="1">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0084</t>
+        </is>
+      </c>
+      <c r="B445" s="5" t="n">
+        <v>46141.66668060185</v>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Astrolabe Chalice Relic</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>An ancient ceremonial chalice with astrolabe mechanisms integrated into the cup, vessel body made of translucent Amber with suspended glowing star maps, brass rim engraved with celestial coordinates, golden stardust swirling inside the cup, ornate brass base with rotating zodiac rings, crystalline charts embedded in stem, warm academic lighting, sharp focus, ritual instrument design, aged brass patina with micro-engraved constellations, layered translucent depth, subtle internal bioluminescent glow, visible handcrafted edge bevels, floating accent fragments, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>astrolabe chalice art, ceremonial astronomy vessel, brass ritual cup, academic astrology artifact, amber star chart goblet, celestial instrument poster, museum quality chalice, golden stardust vessel, antique astronomy relic, zodiac chalice print</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="18" customHeight="1">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0085</t>
+        </is>
+      </c>
+      <c r="B446" s="5" t="n">
+        <v>46141.66673456018</v>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Orrery Lighthouse Beacon</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>A miniature lighthouse tower with mechanical orrery planets orbiting around its beacon chamber, central light made of translucent Amber with glowing star charts projecting outward, brass planetary rings rotating at different levels, golden stardust trails marking orbital paths, crystalline navigation lenses, warm academic lighting, architectural relic design, aged brass with micro-engraved latitude lines, layered translucent depth showing internal gear mechanisms, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>orrery lighthouse poster, architectural astronomy art, brass planetary beacon, celestial navigation tower, amber star chart light, mechanical solar system, academic astrology architecture, golden stardust orbital, museum lighthouse print, vintage orrery design</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="18" customHeight="1">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0086</t>
+        </is>
+      </c>
+      <c r="B447" s="5" t="n">
+        <v>46141.66700450231</v>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Compass Mechanism Blueprint</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>A complex blueprint of an antique brass celestial navigation compass with rotating armillary rings overlaid with cyanotype star charts, metallic silver ink geometric equations mapping constellation paths, ink-wash nebula clouds bleeding through technical diagrams, floating calibration fragments with astronomical annotations, academia aesthetic, vintage cyanotype paper texture with aged edges, museum quality archival presentation, dramatic top lighting casting soft shadows, isolated on white background, composition emphasizes intricate mechanical detail, hyper-detailed mentor-grade object design, primary material system: Cyanotype Paper, Silver Ink, Brass, Crystal Lens, Archival Stock, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>celestial navigation blueprint, astronomical compass art, cyanotype star chart, brass instrument poster, academia aesthetic, vintage scientific diagram, mentor-grade design, archival quality print, constellation mapping, museum collectible wall art</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="18" customHeight="1">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0087</t>
+        </is>
+      </c>
+      <c r="B448" s="5" t="n">
+        <v>46141.66705900463</v>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>Lunar Moth Specimen Blueprint</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>A complex blueprint of a luminous luna moth specimen with spread wings overlaid with cyanotype star charts, metallic silver ink geometric equations mapping wing vein patterns to celestial coordinates, ink-wash nebula clouds bleeding through entomological diagrams, floating scale fragments with taxonomic annotations, academia aesthetic, vintage cyanotype paper texture with aged edges, museum quality archival presentation, dramatic top lighting casting soft shadows, isolated on white background, composition emphasizes symmetrical wing structure, hyper-detailed mentor-grade object design, primary material system: Cyanotype Paper, Silver Ink, Opal Dust, Selenite Crystal, Archival Stock, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>lunar moth blueprint, celestial creature specimen, entomological star chart, cyanotype insect art, bioluminescent design, scientific illustration poster, academia naturalist aesthetic, museum specimen print, ethereal wing diagram, archival quality wall art</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="18" customHeight="1">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0088</t>
+        </is>
+      </c>
+      <c r="B449" s="5" t="n">
+        <v>46141.66710828704</v>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Alchemical Astrolabe Ritual Tool</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>A complex blueprint of an ornate alchemical astrolabe ritual instrument with suspended crystalline rings overlaid with cyanotype star charts, metallic silver ink geometric equations mapping planetary alignments, ink-wash nebula clouds bleeding through hermetic diagrams, floating symbol fragments with esoteric annotations, academia aesthetic, vintage cyanotype paper texture with aged edges, museum quality archival presentation, dramatic top lighting casting soft shadows, isolated on white background, composition emphasizes vertical ceremonial arrangement, hyper-detailed mentor-grade object design, primary material system: Cyanotype Paper, Silver Ink, Rose Quartz, Obsidian, Archival Stock, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>alchemical astrolabe blueprint, ritual instrument design, hermetic star chart, esoteric tool poster, crystalline mechanism art, occult academia aesthetic, planetary alignment diagram, ceremonial object print, archival mystical poster, mentor-grade artifact</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="18" customHeight="1">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0089</t>
+        </is>
+      </c>
+      <c r="B450" s="5" t="n">
+        <v>46141.6671643287</v>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Pagoda Architecture Blueprint</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>A complex blueprint of a multi-tiered celestial pagoda tower with floating platform levels overlaid with cyanotype star charts, metallic silver ink geometric equations mapping sacred geometry proportions, ink-wash nebula clouds bleeding through architectural elevation diagrams, floating roof tile fragments with construction annotations, academia aesthetic, vintage cyanotype paper texture with aged edges, museum quality archival presentation, dramatic top lighting casting soft shadows, isolated on white background, composition emphasizes vertical architectural hierarchy, hyper-detailed mentor-grade object design, primary material system: Cyanotype Paper, Silver Ink, Lapis Lazuli, White Marble, Archival Stock, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>celestial pagoda blueprint, sacred architecture poster, astronomical tower design, cyanotype building diagram, layered structure art, academia architectural aesthetic, sacred geometry print, vertical monument illustration, archival quality poster, mentor-grade design</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="451" ht="18" customHeight="1">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0090</t>
+        </is>
+      </c>
+      <c r="B451" s="5" t="n">
+        <v>46141.66721665509</v>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Starbound Lotus Botanical Blueprint</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>A complex blueprint of an ethereal blooming lotus flower with unfurling petals and exposed root system overlaid with cyanotype star charts, metallic silver ink geometric equations mapping petal fibonacci spirals to cosmic patterns, ink-wash nebula clouds bleeding through botanical cross-section diagrams, floating pollen fragments with celestial annotations, academia aesthetic, vintage cyanotype paper texture with aged edges, museum quality archival presentation, dramatic top lighting casting soft shadows, isolated on white background, composition emphasizes vertical growth axis from root to bloom, hyper-detailed mentor-grade object design, primary material system: Cyanotype Paper, Silver Ink, Pearl Essence, Aquamarine, Archival Stock, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>celestial lotus blueprint, botanical star chart, sacred flower diagram, cyanotype plant anatomy, fibonacci spiral art, ethereal bloom poster, academia botanical aesthetic, scientific illustration print, luminous flora design, archival herbarium wall art</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="18" customHeight="1">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Zen-0001</t>
+        </is>
+      </c>
+      <c r="B452" s="5" t="n">
+        <v>46141.66730649306</v>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Gate of Jade Mist</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>A miniature floating mountain with a bonsai tree made of Imperial Green Jade framed by a Moonstone torii gate, crystalline waterfalls falling into clouds, obsidian rock base, ink-wash nebula backdrop, floating talisman fragments, ethereal zen aesthetic, soft morning mist lighting, isolated on white background, ultra-wide angle, hyper-detailed mentor-grade object design, primary material system: Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>zen bonsai wall art, jade floating mountain poster, moonstone torii gate, celestial asian decor, premium vertical poster, ethereal jade tree, floating mountain art, zen meditation decor, oriental mystical poster, translucent jade artwork</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="18" customHeight="1">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Zen-0002</t>
+        </is>
+      </c>
+      <c r="B453" s="5" t="n">
+        <v>46141.66736773148</v>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Phoenix Flame Ritual Vessel</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>An ornate ceremonial incense burner shaped as a rising phoenix crafted from Imperial Green Jade wings with Moonstone flame accents, floating obsidian smoke wisps, talisman fragments orbiting the vessel, carved feather detail with micro-engraved surface relief, ethereal zen aesthetic, soft morning mist lighting, isolated on white background, ultra-wide angle, hyper-detailed mentor-grade object design, primary material system: Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>phoenix incense burner art, jade ritual vessel poster, ceremonial zen decor, moonstone flame phoenix, oriental vessel artwork, floating obsidian smoke, premium jade phoenix, ritual object wall art, asian ceremonial decor, translucent phoenix poster</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="18" customHeight="1">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Zen-0003</t>
+        </is>
+      </c>
+      <c r="B454" s="5" t="n">
+        <v>46141.66741621528</v>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Lotus Mandala Seal Stone</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>An ancient circular talisman seal carved with blooming lotus mandala pattern in Imperial Green Jade, Moonstone prayer beads wrapped around edges, floating obsidian meditation stones, ink-wash nebula backdrop, sacred geometry micro-engravings, ethereal zen aesthetic, soft morning mist lighting, isolated on white background, ultra-wide angle, hyper-detailed mentor-grade object design, primary material system: Imperial Green Jade, Moonstone, Floating Obsidian, Talisman Fragments, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>lotus mandala seal art, jade talisman poster, sacred geometry decor, moonstone prayer beads, zen meditation seal, oriental mandala artwork, floating stone talisman, premium jade seal, buddhist symbol poster, translucent lotus art</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="18" customHeight="1">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Zen-0004</t>
+        </is>
+      </c>
+      <c r="B455" s="5" t="n">
+        <v>46141.66761756944</v>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Compass Relic</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>An ornate celestial compass made of Imperial Green Jade with obsidian directional markers and amethyst constellation inlays, crystalline water droplets suspended in rotating rings, ethereal zen aesthetic, twilight purple-gold lighting, isolated on white background, three-quarter elevated view, hyper-detailed mentor-grade object design, primary material system: Imperial Green Jade, Floating Obsidian, Amethyst, Crystalline Water, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>zen celestial compass, jade navigation relic, amethyst constellation art, obsidian directional markers, ethereal compass design, twilight mystical artifact, premium spiritual decor, bioluminescent jade object, museum-grade zen art, floating crystal compass, handcrafted celestial instrument, purple-gold lighting poster, translucent jade composition, high-end zen collectible</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="18" customHeight="1">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Zen-0005</t>
+        </is>
+      </c>
+      <c r="B456" s="5" t="n">
+        <v>46141.66766943287</v>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Phoenix Rebirth Vessel</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>An ancient ceremonial vessel shaped as an ascending phoenix with wings made of Imperial Green Jade feathers, obsidian talons gripping amethyst flame base, crystalline water flowing upward in spiral patterns, ethereal zen aesthetic, twilight purple-gold lighting, isolated on white background, dynamic upward spiral composition, hyper-detailed mentor-grade object design, primary material system: Imperial Green Jade, Floating Obsidian, Amethyst, Crystalline Water, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>zen phoenix vessel, jade rebirth sculpture, amethyst flame artifact, obsidian talon design, crystalline water spiral, ethereal bird container, twilight ceremonial art, premium spiritual vessel, bioluminescent phoenix object, museum-grade zen collectible, ascending jade wings, purple-gold mystical poster, translucent feather composition, high-end rebirth symbol</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="18" customHeight="1">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0091</t>
+        </is>
+      </c>
+      <c r="B457" s="5" t="n">
+        <v>46141.66777805555</v>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Jade Lotus Celestial Mechanism</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>A delicate mechanical lotus flower with petals carved from imperial jade and moonstone glass, rotating brass gear core with copper wire stamens, ink-wash constellation patterns etched on translucent petals, floating talisman paper fragments orbiting the bloom, hand-blown glass dewdrops suspended on wire tendrils, illuminated by soft candlelight, academia aesthetic, primary material system: Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>jade lotus mechanism, glass orrery art, celestial botanical sculpture, hand-blown glass flower, copper wire botanical, academia glass art, moonstone petal design, mechanical flower poster, oriental glass craft, museum-grade botanical art, translucent jade sculpture, cinematic wall art, premium vertical poster</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="18" customHeight="1">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0092</t>
+        </is>
+      </c>
+      <c r="B458" s="5" t="n">
+        <v>46141.66783239583</v>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Ceremonial Bell Constellation Vessel</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>An ancient ritual bell crafted from hand-blown moonstone glass with imperial jade clapper, delicate copper wire suspension chains forming orbital patterns, ink-wash celestial maps etched across the translucent surface, talisman paper strips hanging from wire loops, internal bioluminescent glow revealing layered glass construction, flickering candle illumination casting intricate shadows, academia aesthetic, primary material system: Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>ceremonial bell art, glass ritual instrument, moonstone vessel design, copper wire suspension, oriental bell sculpture, academia glass craft, celestial instrument poster, hand-blown ritual object, translucent bell art, museum-grade artifact, premium vertical composition, cinematic ritual art</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="18" customHeight="1">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0093</t>
+        </is>
+      </c>
+      <c r="B459" s="5" t="n">
+        <v>46141.66788685185</v>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Phoenix Feather Armillary Sphere</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>An intricate armillary sphere with individual rings shaped as stylized phoenix feathers, crafted from imperial jade bands and moonstone glass arcs, copper wire meridian lines with ink-wash flame patterns etched on glass surfaces, floating talisman paper ash fragments suspended within the sphere, hand-blown glass orb core glowing from within, single candle casting dramatic shadows through translucent materials, academia aesthetic, primary material system: Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>phoenix armillary sphere, glass celestial instrument, jade feather sculpture, moonstone sphere art, copper meridian design, academia celestial art, mythical creature mechanism, hand-blown sphere poster, oriental astronomy art, museum-grade collectible, premium vertical wall art</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>Ready_for_production</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="18" customHeight="1">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0094</t>
+        </is>
+      </c>
+      <c r="B460" s="5" t="n">
+        <v>46141.66794107639</v>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>Miniature Temple Archive Reliquary</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>A miniature architectural reliquary resembling a sacred temple archive, walls constructed from moonstone glass panels with imperial jade roof tiles, copper wire structural framework forming torii-inspired doorways, ink-wash scripture patterns etched on translucent walls, talisman paper scrolls visible through glass chambers, hand-blown glass foundation with internal glowing compartments, candlelight filtering through multi-layered structure, academia aesthetic, primary material system: Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>temple reliquary art, glass architecture sculpture, miniature shrine design, moonstone temple model, copper framework art, academia architectural relic, oriental building craft, hand-blown structure poster, translucent temple art, museum-grade miniature, premium vertical architecture</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>Ready_for_production</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="18" customHeight="1">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Poster-Academia-0095</t>
+        </is>
+      </c>
+      <c r="B461" s="5" t="n">
+        <v>46141.66798667824</v>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Alchemical Compass Talisman Disc</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>An ornate alchemical compass talisman disc with rotating imperial jade directional markers, moonstone glass face engraved with ink-wash navigation symbols, delicate copper wire pointer arms forming sacred geometry patterns, talisman paper fragments embedded between glass layers, hand-blown glass outer ring with micro-engraved celestial coordinates, illuminated by soft candlelight revealing internal mechanisms, academia aesthetic, primary material system: Hand-blown Glass, Moonstone Glass, Imperial Jade, Copper Wire, Talisman Paper, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, premium matte vertical poster composition, full frame, cinematic lighting, edge-to-edge composition, immersive environment, 12x18 wall art format, --ar 2:3 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>alchemical compass art, glass talisman design, jade navigation disc, moonstone compass poster, copper pointer mechanism, academia seal artifact, oriental compass craft, hand-blown talisman art, translucent disc sculpture, museum-grade compass, premium vertical talisman</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>Ready_for_production</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0081</t>
+        </is>
+      </c>
+      <c r="B462" s="5" t="n">
+        <v>46141.66810224537</v>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Plague Doctor Raven Skull</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>An ornate plague doctor raven skull with elongated brass beak apparatus, Corroded Iron rivets and hinges, Kintsugi gold veins sealing bone fractures, toxic amber bioluminescent vapor seeping from eye sockets, grimdark industrial aesthetic, dramatic underlighting, sharp focus, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: aged bone, Corroded Iron, brass oxidized metal, Kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>plague doctor skull, grimdark alchemy, bioluminescent artifact, kintsugi gold repair, corroded brass apparatus, toxic amber glow, raven bone relic, industrial gothic decor, premium acrylic art, collectible dark fantasy, mentor-grade design, ray traced depth, museum quality sculpture</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0082</t>
+        </is>
+      </c>
+      <c r="B463" s="5" t="n">
+        <v>46141.66815164352</v>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Withered Mandrake Root Chamber</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>A preserved withered mandrake root suspended in geometric glass terrarium chamber, Corroded Iron frame structure, Kintsugi gold veins running through cracked root system, toxic amber bioluminescent preservative fluid pooling at base, grimdark industrial aesthetic, dramatic underlighting, sharp focus, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: desiccated botanical specimen, Corroded Iron, laboratory glass, Kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>alchemical terrarium, preserved mandrake root, grimdark botanical specimen, corroded iron frame, kintsugi gold veins, toxic amber fluid, laboratory relic, industrial apothecary art, premium vertical acrylic, gallery collectible, bioluminescent preservation, mentor-grade design, ray traced glass</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0083</t>
+        </is>
+      </c>
+      <c r="B464" s="5" t="n">
+        <v>46141.66820033565</v>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Ritual Censer Thurible</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>An ancient ritual censer thurible with perforated Corroded Iron shell, cracked heavy glass viewing window, Kintsugi gold veins sealing fractures, toxic amber bioluminescent incense smoke billowing from ornate vents, heavy chain suspension system, grimdark industrial aesthetic, dramatic underlighting, sharp focus, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Corroded Iron, cracked glass, Kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>grimdark thurible, ritual censer artifact, corroded iron incense burner, kintsugi gold repair, toxic amber smoke, bioluminescent vessel, ceremonial relic, industrial gothic design, premium acrylic block, mentor-grade collectible, ray traced depth, museum quality art</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0084</t>
+        </is>
+      </c>
+      <c r="B465" s="5" t="n">
+        <v>46141.66824924768</v>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Collapsed Cathedral Archway Fragment</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>A miniature collapsed cathedral archway fragment with Corroded Iron reinforcement bars exposed, cracked stone masonry, Kintsugi gold veins holding crumbling architecture together, toxic amber bioluminescent moss growing in crevices, grimdark industrial aesthetic, dramatic underlighting, sharp focus, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: weathered stone, Corroded Iron rebar, Kintsugi gold, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>cathedral ruin fragment, grimdark architecture miniature, corroded iron rebar, kintsugi gold restoration, toxic amber moss, bioluminescent decay, Gothic relic art, industrial decay aesthetic, premium acrylic sculpture, mentor-grade collectible, ray traced stone, gallery quality artifact</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Grimdark-0085</t>
+        </is>
+      </c>
+      <c r="B466" s="5" t="n">
+        <v>46141.66829225695</v>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Grimdark Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Alchemist's Divination Compass</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>An ornate alchemist's divination compass with Corroded Iron housing and cracked glass face, Kintsugi gold veins repairing fracture lines, toxic amber bioluminescent liquid filling internal chambers behind rotating brass needle mechanisms, grimdark industrial aesthetic, dramatic underlighting, sharp focus, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Corroded Iron, cracked glass, Kintsugi gold, brass mechanisms, toxic amber bioluminescence, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>alchemical compass, divination instrument, grimdark navigation tool, corroded iron housing, kintsugi gold repair, toxic amber liquid, bioluminescent brass mechanism, industrial occult art, premium acrylic display, mentor-grade design, ray traced glass, gallery collectible talisman</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0001</t>
+        </is>
+      </c>
+      <c r="B467" s="5" t="n">
+        <v>46141.66840614584</v>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Astrolabe Compass Ritual Disc</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>A mechanical astrolabe ritual disc with Moonstone rotating rings and Imperial Jade directional markers, floating compass rose center with glowing constellation pathways, suspended brass gears and crystalline fragments, ink-wash nebula atmosphere swirling through openwork design, isolated on white background, ethereal backlighting, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, brass mechanisms, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>astrolabe compass, celestial navigation, Moonstone ritual disc, Imperial Jade markers, astronomical instrument, academia collectible, mentor-grade artifact, brass mechanism, constellation pathways, premium acrylic art, gallery object, translucent depth, bioluminescent glow, handcrafted precision, museum-grade design</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0002</t>
+        </is>
+      </c>
+      <c r="B468" s="5" t="n">
+        <v>46141.66846547454</v>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Lunar Moth Specimen Chamber</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>A preserved lunar moth creature specimen within Moonstone display chamber dome, wings spread showing Imperial Jade vein patterns and glowing star chart markings, antennae with floating talisman fragments, body segmented with micro-engraved celestial coordinates, ink-wash nebula atmosphere filling bell jar interior, isolated on white background, ethereal backlighting, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, crystalline chitin, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>lunar moth specimen, celestial creature, Moonstone display dome, Imperial Jade wings, entomology art, academia collectible, preserved insect, star chart patterns, bioluminescent specimen, premium acrylic chamber, museum artifact, translucent biology, mentor-grade taxidermy, gallery naturalism</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0003</t>
+        </is>
+      </c>
+      <c r="B469" s="5" t="n">
+        <v>46141.66852152778</v>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Orrery Tree Bonsai</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>A miniature celestial bonsai tree with Moonstone trunk and branches forming orbital paths, Imperial Jade leaves shaped as planetary bodies with glowing astronomical symbols, roots suspended in crystalline soil with floating talisman fragments and stardust particles, ink-wash nebula atmosphere pooling around base, isolated on white background, ethereal backlighting, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, crystalline minerals, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>orrery bonsai, celestial tree, Moonstone trunk, Imperial Jade planets, botanical astronomy, miniature cosmos, academia plant, orbital branches, crystalline roots, premium acrylic sculpture, mentor-grade horticulture, translucent foliage, bioluminescent leaves, gallery botanical art</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0004</t>
+        </is>
+      </c>
+      <c r="B470" s="5" t="n">
+        <v>46141.66857056713</v>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Observatory Tower Fragment Relic</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>An ancient observatory tower architectural fragment with Moonstone spiral staircase winding around central axis, Imperial Jade telescope lens at apex with glowing star projections, crumbling walls revealing floating talisman fragments and constellation maps, ink-wash nebula atmosphere flowing through archways and windows, isolated on white background, ethereal backlighting, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, weathered stone, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>observatory relic, architectural fragment, Moonstone tower, Imperial Jade telescope, celestial ruins, academia architecture, spiral staircase, astronomical monument, weathered stone, premium acrylic sculpture, mentor-grade ruin, translucent structure, ancient observatory, gallery collectible</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>Defeated_Timeout</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Academia-0005</t>
+        </is>
+      </c>
+      <c r="B471" s="5" t="n">
+        <v>46141.66862112268</v>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Academia Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Alchemical Star Flask Vessel</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>An ornate alchemical flask vessel with Moonstone body and Imperial Jade stopper, interior filled with swirling liquid cosmos containing miniature galaxies and floating talisman fragments, geometric sacred patterns etched into surface with glowing star coordinates, suspended droplets of luminous nebula essence, ink-wash nebula atmosphere emanating from opening, isolated on white background, ethereal backlighting, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, liquid cosmos, ink-wash nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>alchemical flask, star vessel, Moonstone container, Imperial Jade stopper, liquid cosmos, celestial potion, academia alchemy, contained universe, sacred geometry, premium acrylic bottle, mentor-grade glasswork, translucent elixir, bioluminescent fluid, gallery apothecary art</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0001</t>
+        </is>
+      </c>
+      <c r="B472" s="5" t="n">
+        <v>46141.66874277778</v>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Crane Guardian Mechanism</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>A mechanical origami crane with folding wings of brushed moonstone and imperial jade, clockwork joints with aquamarine crystal hinges, ink-wash nebula patterns flowing across wing panels, floating talisman fragments orbiting the body, zen-cyber aesthetic, soft blue and violet bioluminescence, celestial mist, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>mechanical crane, origami sculpture, moonstone wings, jade clockwork, aquamarine crystals, zen cyberpunk, bioluminescent art, floating fragments, celestial mist, premium acrylic block, collectible artifact, translucent depth, museum grade lighting</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0002</t>
+        </is>
+      </c>
+      <c r="B473" s="5" t="n">
+        <v>46141.66879206018</v>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Ritual Bell Shrine</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>An ancient meditation bell with body crafted from brushed moonstone and imperial jade panels, clockwork brass suspension mount, glowing aquamarine prayer beads spiraling around the bell, ink-wash nebula patterns etched into surface, floating talisman fragments circling the artifact, zen-cyber aesthetic, soft blue and violet bioluminescence, celestial mist, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>meditation bell, ritual instrument, moonstone panels, jade craftsmanship, prayer beads, aquamarine glow, zen architecture, floating talismans, celestial artifact, premium collectible, translucent layers, museum quality, handcrafted details</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0003</t>
+        </is>
+      </c>
+      <c r="B474" s="5" t="n">
+        <v>46141.66884230324</v>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Pagoda Fragment Relic</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>A floating miniature pagoda tower section with walls of brushed moonstone and imperial jade, clockwork brass structural framework, aquamarine crystal windows glowing from within, ink-wash nebula patterns swirling through interior chambers, floating talisman fragments orbiting the structure, zen-cyber aesthetic, soft blue and violet bioluminescence, celestial mist, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>pagoda architecture, floating tower, moonstone walls, jade framework, aquamarine windows, clockwork brass, zen relic, celestial structure, bioluminescent interior, premium art object, layered depth, gallery collectible, architectural fragment</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0004</t>
+        </is>
+      </c>
+      <c r="B475" s="5" t="n">
+        <v>46141.66888943287</v>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Koi Automaton Spirit</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>A mechanical koi fish with segmented armor plates of brushed moonstone and imperial jade, clockwork brass joints and gears visible at articulation points, aquamarine crystal scales catching light, ink-wash nebula patterns flowing along body, floating talisman fragments following the fish, zen-cyber aesthetic, soft blue and violet bioluminescence, celestial mist, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>mechanical koi, automaton fish, moonstone armor, jade segments, aquamarine scales, clockwork creature, zen cyberpunk, bioluminescent design, floating talismans, premium sculpture, translucent materials, collectible art, handcrafted details</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0005</t>
+        </is>
+      </c>
+      <c r="B476" s="5" t="n">
+        <v>46141.66893707176</v>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Incense Vessel Constellation</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>An ornate incense burner with spherical body of brushed moonstone and imperial jade segments, clockwork brass lid mechanism with rotating celestial patterns, aquamarine crystal smoke vents glowing softly, ink-wash nebula patterns emerging as ethereal vapor, floating talisman fragments suspended above the vessel, zen-cyber aesthetic, soft blue and violet bioluminescence, celestial mist, macro photography, isolated on white background, hyper-detailed mentor-grade object design, primary material system: Moonstone, Imperial Jade, Aquamarine, Brushed Metal, Clockwork Brass, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>incense burner, ritual vessel, moonstone sphere, jade segments, aquamarine vents, clockwork mechanism, zen container, celestial vapor, bioluminescent glow, premium artifact, translucent design, museum collectible, handcrafted luxury</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0006</t>
+        </is>
+      </c>
+      <c r="B477" s="5" t="n">
+        <v>46141.66907775463</v>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Jade Phoenix Incense Altar</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>A ceremonial phoenix sculpture carved from imperial jade perched on a floating incense altar, wings spread in flight pose with moonstone feather inlays, rising smoke forming zen calligraphy symbols, ink-wash nebula background, scattered lotus petal fragments, zen aesthetic, soft celestial glow, bamboo silhouette fading into mist, , 3D relief effect, solid white background isolated on white background, hyper-detailed mentor-grade object design, primary material system: Imperial Jade, Moonstone, Raku Pottery Base, Emerald Smoke, Ink-Wash Nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>jade phoenix sculpture, zen incense altar, moonstone inlay art, imperial jade carving, ceremonial tea decor, ink-wash nebula aesthetic, floating lotus fragments, bioluminescent glow, kintsugi vein detail, museum-grade collectible, mentor-grade zen object, celestial phoenix totem, raku pottery base, translucent depth acrylic</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0007</t>
+        </is>
+      </c>
+      <c r="B478" s="5" t="n">
+        <v>46141.66914354167</v>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Sacred Lotus Meditation Bell</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>An ancient bronze meditation bell shaped as blooming lotus flower with rough raku pottery clapper, moonstone dewdrops on petals, imperial jade stem wrapped in silk cord, sound wave ripples visualized as ink-wash nebula rings, floating prayer beads orbiting, zen aesthetic, soft celestial glow, bamboo forest silhouette fading into mist, , 3D relief effect, solid white background isolated on white background, hyper-detailed mentor-grade object design, primary material system: Aged Bronze, Rough Raku Pottery, Moonstone, Imperial Jade, Ink-Wash Nebula, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>lotus meditation bell, bronze ritual instrument, raku pottery clapper, moonstone dewdrops, sacred sound visualization, zen prayer beads, imperial jade stem, ink-wash sound waves, bioluminescent lotus art, handcrafted bronze bell, kintsugi detail work, celestial glow artifact, museum-quality bell sculpture, translucent acrylic depth</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0008</t>
+        </is>
+      </c>
+      <c r="B479" s="5" t="n">
+        <v>46141.66920890046</v>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Celestial Bonsai Moon Garden</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>A miniature celestial bonsai tree growing from crescent moon-shaped rough raku pottery vessel, branches made of twisted imperial jade wire with moonstone blossoms, roots visible through translucent vessel walls, ink-wash nebula soil glowing softly, floating stone lantern fragments, zen aesthetic, soft celestial glow, bamboo forest silhouette fading into mist, , 3D relief effect, solid white background isolated on white background, hyper-detailed mentor-grade object design, primary material system: Rough Raku Pottery, Imperial Jade Wire, Moonstone Blossoms, Luminous Nebula Soil, Ink-Wash Mist, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>celestial bonsai sculpture, crescent moon vessel, imperial jade branches, moonstone blossom tree, raku pottery planter, luminous nebula soil, floating lantern fragments, translucent root system, zen garden miniature, bioluminescent botanical art, kintsugi vessel detail, museum-grade bonsai object, handcrafted jade wire, premium acrylic composition</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0009</t>
+        </is>
+      </c>
+      <c r="B480" s="5" t="n">
+        <v>46141.66946560185</v>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Whispering Bamboo Flute</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>A floating shakuhachi bamboo flute made of aged bamboo with natural nodes and grain texture in warm honey tones, ethereal mist spiraling from the mouthpiece forming delicate kanji characters, zen garden stones arranged in contemplative pattern below, soft morning light filtering through translucent fog, serene meditation aesthetic, wisps of pale jade vapor, , 3D relief effect, solid white background isolated on white background, hyper-detailed mentor-grade object design, primary material system: Aged Bamboo, Honey Tones, Jade Vapor, Morning Light, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>zen bamboo flute meditation, shakuhachi spiritual art, japanese bamboo instrument, contemplative music decor, mindfulness ritual object, asian meditation gift, bamboo grain texture, ethereal mist design, serene morning light, premium zen collectible, museum-grade oriental art, handcrafted bamboo aesthetic, tranquil spiritual decor</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic-Zen-0010</t>
+        </is>
+      </c>
+      <c r="B481" s="5" t="n">
+        <v>46141.66953841435</v>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>Zen</t>
+        </is>
+      </c>
+      <c r="D481" s="2" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="E481" s="2" t="inlineStr">
+        <is>
+          <t>Zen Mentor-Grade</t>
+        </is>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>Lotus Seed Pod Vessel</t>
+        </is>
+      </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>A floating dried lotus seed pod vessel in weathered terracotta and dusty sage tones, intricate honeycomb pattern of seed chambers visible, delicate golden pollen particles suspended in air around it, reflected in still water surface below creating mirror symmetry, warm sunset amber glow, botanical zen aesthetic, traces of burnt umber patina, , 3D relief effect, solid white background isolated on white background, hyper-detailed mentor-grade object design, primary material system: Dried Lotus Pod, Terracotta Patina, Golden Pollen, Amber Reflection, micro-engraved surface relief, visible handcrafted edge bevels, layered translucent depth, subtle internal bioluminescent glow, refined kintsugi-like vein logic, floating accent fragments arranged with intentional negative space, cinematic rim lighting plus soft museum-grade overhead fill, crisp silhouette readability, centered premium product composition, clean contour separation, high-end collectible artifact aesthetic, isolated on white background, premium vertical acrylic photo block composition, 3D depth, refractive light, internal glow, ray tracing, gallery collectible art object, --ar 5:7 --v 6.1 --style raw --no skin, person, text, watermark</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>lotus seed pod art, botanical zen decor, dried lotus vessel, nature meditation object, organic texture design, terracotta patina aesthetic, golden pollen particles, sunset reflection art, sacred botanical gift, premium nature collectible, museum-grade botanical art, contemplative seed pod, tranquil organic sculpture</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I461"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Database/Production_Line.xlsx
+++ b/Database/Production_Line.xlsx
@@ -5338,7 +5338,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Ready_for_production</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
